--- a/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
@@ -1601,13 +1601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F67CC530-11B0-4942-A174-AFF05FD51805}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{336EF14E-7E91-4F68-82F6-AE588E14F981}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE23567-F36A-44B8-8832-B11376E31346}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A70347E5-F163-45FB-893A-9F0926EA353E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C066B21-6075-4914-8152-5F2C7BA9A0BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52080C80-7F27-4B09-A301-CA0369CD864D}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
@@ -1601,13 +1601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{336EF14E-7E91-4F68-82F6-AE588E14F981}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7EFB46-B1F5-4BA3-BA9D-7C7C8B0D39D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A70347E5-F163-45FB-893A-9F0926EA353E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E1C94DD-EC8F-4895-9171-79E04610FA25}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52080C80-7F27-4B09-A301-CA0369CD864D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0955C313-D32B-47C5-9914-C7B92AC95D67}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Unit_Measure_Records.xlsx
@@ -1601,13 +1601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7EFB46-B1F5-4BA3-BA9D-7C7C8B0D39D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F67CC530-11B0-4942-A174-AFF05FD51805}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E1C94DD-EC8F-4895-9171-79E04610FA25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCE23567-F36A-44B8-8832-B11376E31346}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0955C313-D32B-47C5-9914-C7B92AC95D67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C066B21-6075-4914-8152-5F2C7BA9A0BC}"/>
 </file>